--- a/artfynd/A 16114-2025 artfynd.xlsx
+++ b/artfynd/A 16114-2025 artfynd.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Markus Borja, Joel Helker-Nygren</t>
+          <t>Joel Helker-Nygren, Markus Borja</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 16114-2025 artfynd.xlsx
+++ b/artfynd/A 16114-2025 artfynd.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren, Markus Borja</t>
+          <t>Markus Borja, Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 16114-2025 artfynd.xlsx
+++ b/artfynd/A 16114-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129454997</v>
       </c>
       <c r="B2" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129455167</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129455020</v>
       </c>
       <c r="B4" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>129455512</v>
       </c>
       <c r="B5" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>129455066</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 16114-2025 artfynd.xlsx
+++ b/artfynd/A 16114-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129454997</v>
       </c>
       <c r="B2" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129455167</v>
       </c>
       <c r="B3" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129455020</v>
       </c>
       <c r="B4" t="n">
-        <v>57890</v>
+        <v>57895</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>129455512</v>
       </c>
       <c r="B5" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>129455066</v>
       </c>
       <c r="B6" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 16114-2025 artfynd.xlsx
+++ b/artfynd/A 16114-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129454997</v>
       </c>
       <c r="B2" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129455167</v>
       </c>
       <c r="B3" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129455020</v>
       </c>
       <c r="B4" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>129455512</v>
       </c>
       <c r="B5" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>129455066</v>
       </c>
       <c r="B6" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
